--- a/artfynd/A 21848-2024 artfynd.xlsx
+++ b/artfynd/A 21848-2024 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117730582</v>
+        <v>117730565</v>
       </c>
       <c r="B11" t="n">
-        <v>97857</v>
+        <v>98170</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>219880</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448099</v>
+        <v>448101</v>
       </c>
       <c r="R11" t="n">
-        <v>7032637</v>
+        <v>7032728</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117730565</v>
+        <v>117730582</v>
       </c>
       <c r="B12" t="n">
-        <v>98170</v>
+        <v>97857</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219880</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448101</v>
+        <v>448099</v>
       </c>
       <c r="R12" t="n">
-        <v>7032728</v>
+        <v>7032637</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 21848-2024 artfynd.xlsx
+++ b/artfynd/A 21848-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117730563</v>
+        <v>117730555</v>
       </c>
       <c r="B2" t="n">
-        <v>82259</v>
+        <v>90499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448120</v>
+        <v>448135</v>
       </c>
       <c r="R2" t="n">
-        <v>7032728</v>
+        <v>7032690</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117730579</v>
+        <v>117730569</v>
       </c>
       <c r="B3" t="n">
         <v>78480</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448075</v>
+        <v>448062</v>
       </c>
       <c r="R3" t="n">
-        <v>7032651</v>
+        <v>7032720</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117730555</v>
+        <v>117730568</v>
       </c>
       <c r="B5" t="n">
-        <v>90499</v>
+        <v>74592</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448135</v>
+        <v>448086</v>
       </c>
       <c r="R5" t="n">
-        <v>7032690</v>
+        <v>7032723</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117730568</v>
+        <v>117730548</v>
       </c>
       <c r="B6" t="n">
-        <v>74592</v>
+        <v>77417</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448086</v>
+        <v>448169</v>
       </c>
       <c r="R6" t="n">
-        <v>7032723</v>
+        <v>7032634</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117730561</v>
+        <v>117730581</v>
       </c>
       <c r="B7" t="n">
-        <v>77417</v>
+        <v>74592</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448119</v>
+        <v>448096</v>
       </c>
       <c r="R7" t="n">
-        <v>7032707</v>
+        <v>7032652</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117730548</v>
+        <v>117730551</v>
       </c>
       <c r="B8" t="n">
-        <v>77417</v>
+        <v>98170</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>219880</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448169</v>
+        <v>448143</v>
       </c>
       <c r="R8" t="n">
-        <v>7032634</v>
+        <v>7032661</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117730571</v>
+        <v>117730576</v>
       </c>
       <c r="B9" t="n">
-        <v>90499</v>
+        <v>82259</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448067</v>
+        <v>448076</v>
       </c>
       <c r="R9" t="n">
-        <v>7032673</v>
+        <v>7032649</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117730576</v>
+        <v>117730574</v>
       </c>
       <c r="B10" t="n">
-        <v>82259</v>
+        <v>77417</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448076</v>
+        <v>448074</v>
       </c>
       <c r="R10" t="n">
-        <v>7032649</v>
+        <v>7032651</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117730565</v>
+        <v>117730582</v>
       </c>
       <c r="B11" t="n">
-        <v>98170</v>
+        <v>97857</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219880</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448101</v>
+        <v>448099</v>
       </c>
       <c r="R11" t="n">
-        <v>7032728</v>
+        <v>7032637</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117730582</v>
+        <v>117730554</v>
       </c>
       <c r="B12" t="n">
         <v>97857</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448099</v>
+        <v>448137</v>
       </c>
       <c r="R12" t="n">
-        <v>7032637</v>
+        <v>7032675</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117730550</v>
+        <v>117730572</v>
       </c>
       <c r="B13" t="n">
         <v>78480</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448167</v>
+        <v>448056</v>
       </c>
       <c r="R13" t="n">
-        <v>7032635</v>
+        <v>7032665</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117730580</v>
+        <v>117730563</v>
       </c>
       <c r="B14" t="n">
-        <v>78480</v>
+        <v>82259</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448096</v>
+        <v>448120</v>
       </c>
       <c r="R14" t="n">
-        <v>7032652</v>
+        <v>7032728</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117730554</v>
+        <v>117730547</v>
       </c>
       <c r="B15" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448137</v>
+        <v>448169</v>
       </c>
       <c r="R15" t="n">
-        <v>7032675</v>
+        <v>7032634</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117730573</v>
+        <v>117730561</v>
       </c>
       <c r="B16" t="n">
-        <v>74592</v>
+        <v>77417</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448076</v>
+        <v>448119</v>
       </c>
       <c r="R16" t="n">
-        <v>7032653</v>
+        <v>7032707</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,7 +2355,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117730549</v>
+        <v>117730562</v>
       </c>
       <c r="B17" t="n">
         <v>74592</v>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448169</v>
+        <v>448119</v>
       </c>
       <c r="R17" t="n">
-        <v>7032634</v>
+        <v>7032707</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117730564</v>
+        <v>117730580</v>
       </c>
       <c r="B18" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448104</v>
+        <v>448096</v>
       </c>
       <c r="R18" t="n">
-        <v>7032729</v>
+        <v>7032652</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117730581</v>
+        <v>117730564</v>
       </c>
       <c r="B19" t="n">
-        <v>74592</v>
+        <v>97857</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,25 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448096</v>
+        <v>448104</v>
       </c>
       <c r="R19" t="n">
-        <v>7032652</v>
+        <v>7032729</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117730574</v>
+        <v>117730559</v>
       </c>
       <c r="B20" t="n">
-        <v>77417</v>
+        <v>97857</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448074</v>
+        <v>448114</v>
       </c>
       <c r="R20" t="n">
-        <v>7032651</v>
+        <v>7032697</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117730551</v>
+        <v>117730571</v>
       </c>
       <c r="B21" t="n">
-        <v>98170</v>
+        <v>90499</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219880</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448143</v>
+        <v>448067</v>
       </c>
       <c r="R21" t="n">
-        <v>7032661</v>
+        <v>7032673</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117730547</v>
+        <v>117730565</v>
       </c>
       <c r="B22" t="n">
-        <v>78480</v>
+        <v>98170</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2927,25 +2927,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448169</v>
+        <v>448101</v>
       </c>
       <c r="R22" t="n">
-        <v>7032634</v>
+        <v>7032728</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117730572</v>
+        <v>117730567</v>
       </c>
       <c r="B23" t="n">
-        <v>78480</v>
+        <v>77417</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448056</v>
+        <v>448086</v>
       </c>
       <c r="R23" t="n">
-        <v>7032665</v>
+        <v>7032723</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117730559</v>
+        <v>117730573</v>
       </c>
       <c r="B25" t="n">
-        <v>97857</v>
+        <v>74592</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,25 +3263,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448114</v>
+        <v>448076</v>
       </c>
       <c r="R25" t="n">
-        <v>7032697</v>
+        <v>7032653</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,7 +3363,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117730569</v>
+        <v>117730550</v>
       </c>
       <c r="B26" t="n">
         <v>78480</v>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448062</v>
+        <v>448167</v>
       </c>
       <c r="R26" t="n">
-        <v>7032720</v>
+        <v>7032635</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117730562</v>
+        <v>117730579</v>
       </c>
       <c r="B27" t="n">
-        <v>74592</v>
+        <v>78480</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448119</v>
+        <v>448075</v>
       </c>
       <c r="R27" t="n">
-        <v>7032707</v>
+        <v>7032651</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117730567</v>
+        <v>117730549</v>
       </c>
       <c r="B28" t="n">
-        <v>77417</v>
+        <v>74592</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448086</v>
+        <v>448169</v>
       </c>
       <c r="R28" t="n">
-        <v>7032723</v>
+        <v>7032634</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 21848-2024 artfynd.xlsx
+++ b/artfynd/A 21848-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117730555</v>
+        <v>117730559</v>
       </c>
       <c r="B2" t="n">
-        <v>90499</v>
+        <v>97859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448135</v>
+        <v>448114</v>
       </c>
       <c r="R2" t="n">
-        <v>7032690</v>
+        <v>7032697</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117730569</v>
+        <v>117730576</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>82261</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448062</v>
+        <v>448076</v>
       </c>
       <c r="R3" t="n">
-        <v>7032720</v>
+        <v>7032649</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>117730570</v>
       </c>
       <c r="B4" t="n">
-        <v>78564</v>
+        <v>78566</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117730568</v>
+        <v>117730572</v>
       </c>
       <c r="B5" t="n">
-        <v>74592</v>
+        <v>78482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448086</v>
+        <v>448056</v>
       </c>
       <c r="R5" t="n">
-        <v>7032723</v>
+        <v>7032665</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117730548</v>
+        <v>117730579</v>
       </c>
       <c r="B6" t="n">
-        <v>77417</v>
+        <v>78482</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448169</v>
+        <v>448075</v>
       </c>
       <c r="R6" t="n">
-        <v>7032634</v>
+        <v>7032651</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117730581</v>
+        <v>117730571</v>
       </c>
       <c r="B7" t="n">
-        <v>74592</v>
+        <v>90501</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448096</v>
+        <v>448067</v>
       </c>
       <c r="R7" t="n">
-        <v>7032652</v>
+        <v>7032673</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117730551</v>
+        <v>117730563</v>
       </c>
       <c r="B8" t="n">
-        <v>98170</v>
+        <v>82261</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448143</v>
+        <v>448120</v>
       </c>
       <c r="R8" t="n">
-        <v>7032661</v>
+        <v>7032728</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117730576</v>
+        <v>117730567</v>
       </c>
       <c r="B9" t="n">
-        <v>82259</v>
+        <v>77419</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448076</v>
+        <v>448086</v>
       </c>
       <c r="R9" t="n">
-        <v>7032649</v>
+        <v>7032723</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117730574</v>
+        <v>117730551</v>
       </c>
       <c r="B10" t="n">
-        <v>77417</v>
+        <v>98172</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>219880</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448074</v>
+        <v>448143</v>
       </c>
       <c r="R10" t="n">
-        <v>7032651</v>
+        <v>7032661</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117730582</v>
+        <v>117730554</v>
       </c>
       <c r="B11" t="n">
-        <v>97857</v>
+        <v>97859</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448099</v>
+        <v>448137</v>
       </c>
       <c r="R11" t="n">
-        <v>7032637</v>
+        <v>7032675</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117730554</v>
+        <v>117730550</v>
       </c>
       <c r="B12" t="n">
-        <v>97857</v>
+        <v>78482</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448137</v>
+        <v>448167</v>
       </c>
       <c r="R12" t="n">
-        <v>7032675</v>
+        <v>7032635</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117730572</v>
+        <v>117730573</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>74594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448056</v>
+        <v>448076</v>
       </c>
       <c r="R13" t="n">
-        <v>7032665</v>
+        <v>7032653</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117730563</v>
+        <v>117730581</v>
       </c>
       <c r="B14" t="n">
-        <v>82259</v>
+        <v>74594</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448120</v>
+        <v>448096</v>
       </c>
       <c r="R14" t="n">
-        <v>7032728</v>
+        <v>7032652</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117730547</v>
+        <v>117730565</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>98172</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448169</v>
+        <v>448101</v>
       </c>
       <c r="R15" t="n">
-        <v>7032634</v>
+        <v>7032728</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117730561</v>
+        <v>117730560</v>
       </c>
       <c r="B16" t="n">
-        <v>77417</v>
+        <v>78482</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448119</v>
+        <v>448124</v>
       </c>
       <c r="R16" t="n">
-        <v>7032707</v>
+        <v>7032710</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117730562</v>
+        <v>117730568</v>
       </c>
       <c r="B17" t="n">
-        <v>74592</v>
+        <v>74594</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448119</v>
+        <v>448086</v>
       </c>
       <c r="R17" t="n">
-        <v>7032707</v>
+        <v>7032723</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117730580</v>
+        <v>117730574</v>
       </c>
       <c r="B18" t="n">
-        <v>78480</v>
+        <v>77419</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448096</v>
+        <v>448074</v>
       </c>
       <c r="R18" t="n">
-        <v>7032652</v>
+        <v>7032651</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117730564</v>
+        <v>117730548</v>
       </c>
       <c r="B19" t="n">
-        <v>97857</v>
+        <v>77419</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,25 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448104</v>
+        <v>448169</v>
       </c>
       <c r="R19" t="n">
-        <v>7032729</v>
+        <v>7032634</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117730559</v>
+        <v>117730582</v>
       </c>
       <c r="B20" t="n">
-        <v>97857</v>
+        <v>97859</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448114</v>
+        <v>448099</v>
       </c>
       <c r="R20" t="n">
-        <v>7032697</v>
+        <v>7032637</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117730571</v>
+        <v>117730555</v>
       </c>
       <c r="B21" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448067</v>
+        <v>448135</v>
       </c>
       <c r="R21" t="n">
-        <v>7032673</v>
+        <v>7032690</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117730565</v>
+        <v>117730549</v>
       </c>
       <c r="B22" t="n">
-        <v>98170</v>
+        <v>74594</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2927,25 +2927,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219880</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448101</v>
+        <v>448169</v>
       </c>
       <c r="R22" t="n">
-        <v>7032728</v>
+        <v>7032634</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117730567</v>
+        <v>117730562</v>
       </c>
       <c r="B23" t="n">
-        <v>77417</v>
+        <v>74594</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448086</v>
+        <v>448119</v>
       </c>
       <c r="R23" t="n">
-        <v>7032723</v>
+        <v>7032707</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117730560</v>
+        <v>117730580</v>
       </c>
       <c r="B24" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448124</v>
+        <v>448096</v>
       </c>
       <c r="R24" t="n">
-        <v>7032710</v>
+        <v>7032652</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117730573</v>
+        <v>117730561</v>
       </c>
       <c r="B25" t="n">
-        <v>74592</v>
+        <v>77419</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448076</v>
+        <v>448119</v>
       </c>
       <c r="R25" t="n">
-        <v>7032653</v>
+        <v>7032707</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117730550</v>
+        <v>117730547</v>
       </c>
       <c r="B26" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448167</v>
+        <v>448169</v>
       </c>
       <c r="R26" t="n">
-        <v>7032635</v>
+        <v>7032634</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117730579</v>
+        <v>117730564</v>
       </c>
       <c r="B27" t="n">
-        <v>78480</v>
+        <v>97859</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,25 +3487,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448075</v>
+        <v>448104</v>
       </c>
       <c r="R27" t="n">
-        <v>7032651</v>
+        <v>7032729</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117730549</v>
+        <v>117730569</v>
       </c>
       <c r="B28" t="n">
-        <v>74592</v>
+        <v>78482</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448169</v>
+        <v>448062</v>
       </c>
       <c r="R28" t="n">
-        <v>7032634</v>
+        <v>7032720</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 21848-2024 artfynd.xlsx
+++ b/artfynd/A 21848-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117730579</v>
+        <v>117730571</v>
       </c>
       <c r="B6" t="n">
-        <v>78482</v>
+        <v>90501</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448075</v>
+        <v>448067</v>
       </c>
       <c r="R6" t="n">
-        <v>7032651</v>
+        <v>7032673</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117730571</v>
+        <v>117730563</v>
       </c>
       <c r="B7" t="n">
-        <v>90501</v>
+        <v>82261</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448067</v>
+        <v>448120</v>
       </c>
       <c r="R7" t="n">
-        <v>7032673</v>
+        <v>7032728</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117730563</v>
+        <v>117730579</v>
       </c>
       <c r="B8" t="n">
-        <v>82261</v>
+        <v>78482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448120</v>
+        <v>448075</v>
       </c>
       <c r="R8" t="n">
-        <v>7032728</v>
+        <v>7032651</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
